--- a/tutorials/data/heat_demand_input_chp_bhp.xlsx
+++ b/tutorials/data/heat_demand_input_chp_bhp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eprade\Git\pandaprosumer_OS\tutorials\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carl\PycharmProjects\pandaprosumer\tutorials\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA315044-DC2E-4DF9-9B90-891324834761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FADF2BEE-AA32-4CFB-AC25-E81C2443848F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>cycle</t>
   </si>
@@ -43,6 +43,12 @@
   </si>
   <si>
     <t>t_source_k</t>
+  </si>
+  <si>
+    <t>p_el_bhp</t>
+  </si>
+  <si>
+    <t>p_el_chp</t>
   </si>
 </sst>
 </file>
@@ -370,17 +376,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F290"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H290"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="5.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.53515625" customWidth="1"/>
+    <col min="3" max="3" width="12.3046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.84375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.3046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -399,8 +405,14 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="1">
         <v>0</v>
       </c>
@@ -414,13 +426,19 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>280</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" s="1">
         <v>1.0416666666666666E-2</v>
       </c>
@@ -434,13 +452,19 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>280</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" s="1">
         <v>2.0833333333333301E-2</v>
       </c>
@@ -454,13 +478,19 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>280</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" s="1">
         <v>3.125E-2</v>
       </c>
@@ -474,13 +504,19 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
         <v>280</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" s="1">
         <v>4.1666666666666699E-2</v>
       </c>
@@ -494,13 +530,19 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
         <v>280</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="1">
         <v>5.2083333333333301E-2</v>
       </c>
@@ -514,13 +556,19 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>280</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" s="1">
         <v>6.25E-2</v>
       </c>
@@ -534,13 +582,19 @@
         <v>0</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8">
         <v>280</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" s="1">
         <v>7.2916666666666699E-2</v>
       </c>
@@ -554,13 +608,19 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F9">
         <v>280</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="1">
         <v>8.3333333333333301E-2</v>
       </c>
@@ -574,13 +634,19 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10">
         <v>280</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" s="1">
         <v>9.375E-2</v>
       </c>
@@ -594,13 +660,19 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11">
         <v>280</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" s="1">
         <v>0.104166666666667</v>
       </c>
@@ -614,13 +686,19 @@
         <v>0</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F12">
         <v>280</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" s="1">
         <v>0.114583333333333</v>
       </c>
@@ -634,13 +712,19 @@
         <v>0</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13">
         <v>280</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="1">
         <v>0.125</v>
       </c>
@@ -654,13 +738,19 @@
         <v>0</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
         <v>280</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="1">
         <v>0.13541666666666699</v>
       </c>
@@ -674,13 +764,19 @@
         <v>0</v>
       </c>
       <c r="E15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15">
         <v>280</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" s="1">
         <v>0.14583333333333301</v>
       </c>
@@ -694,13 +790,19 @@
         <v>0</v>
       </c>
       <c r="E16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F16">
         <v>280</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" s="1">
         <v>0.15625</v>
       </c>
@@ -714,13 +816,19 @@
         <v>0</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17">
         <v>280</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="1">
         <v>0.16666666666666699</v>
       </c>
@@ -734,13 +842,19 @@
         <v>0</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
         <v>280</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" s="1">
         <v>0.17708333333333301</v>
       </c>
@@ -754,13 +868,19 @@
         <v>0</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19">
         <v>280</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" s="1">
         <v>0.1875</v>
       </c>
@@ -774,13 +894,19 @@
         <v>0</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20">
         <v>280</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" s="1">
         <v>0.19791666666666699</v>
       </c>
@@ -794,13 +920,19 @@
         <v>0</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F21">
         <v>280</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" s="1">
         <v>0.20833333333333301</v>
       </c>
@@ -814,13 +946,19 @@
         <v>0</v>
       </c>
       <c r="E22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22">
         <v>280</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="1">
         <v>0.21875</v>
       </c>
@@ -834,13 +972,19 @@
         <v>0</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F23">
         <v>280</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" s="1">
         <v>0.22916666666666699</v>
       </c>
@@ -854,13 +998,19 @@
         <v>0</v>
       </c>
       <c r="E24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24">
         <v>280</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" s="1">
         <v>0.23958333333333301</v>
       </c>
@@ -874,13 +1024,19 @@
         <v>0</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F25">
         <v>280</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" s="1">
         <v>0.25</v>
       </c>
@@ -894,13 +1050,19 @@
         <v>500</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F26">
         <v>280</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="1">
         <v>0.26041666666666702</v>
       </c>
@@ -914,13 +1076,19 @@
         <v>500</v>
       </c>
       <c r="E27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27">
         <v>280</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" s="1">
         <v>0.27083333333333298</v>
       </c>
@@ -934,13 +1102,19 @@
         <v>500</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28">
         <v>280</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" s="1">
         <v>0.28125</v>
       </c>
@@ -954,13 +1128,19 @@
         <v>500</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29">
         <v>280</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" s="1">
         <v>0.29166666666666702</v>
       </c>
@@ -974,13 +1154,19 @@
         <v>500</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>280</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" s="1">
         <v>0.30208333333333298</v>
       </c>
@@ -994,13 +1180,19 @@
         <v>500</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F31">
         <v>280</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" s="1">
         <v>0.3125</v>
       </c>
@@ -1014,13 +1206,19 @@
         <v>500</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F32">
         <v>280</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" s="1">
         <v>0.32291666666666702</v>
       </c>
@@ -1034,13 +1232,19 @@
         <v>500</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33">
         <v>280</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" s="1">
         <v>0.33333333333333298</v>
       </c>
@@ -1054,13 +1258,19 @@
         <v>500</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F34">
         <v>280</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" s="1">
         <v>0.34375</v>
       </c>
@@ -1074,13 +1284,19 @@
         <v>1200</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F35">
         <v>280</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" s="1">
         <v>0.35416666666666702</v>
       </c>
@@ -1094,13 +1310,19 @@
         <v>1200</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36">
         <v>290</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" s="1">
         <v>0.36458333333333298</v>
       </c>
@@ -1114,13 +1336,19 @@
         <v>1200</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37">
         <v>290</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" s="1">
         <v>0.375</v>
       </c>
@@ -1134,13 +1362,19 @@
         <v>1200</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38">
         <v>290</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" s="1">
         <v>0.38541666666666702</v>
       </c>
@@ -1154,13 +1388,19 @@
         <v>1200</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39">
         <v>290</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" s="1">
         <v>0.39583333333333298</v>
       </c>
@@ -1174,13 +1414,19 @@
         <v>1200</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
         <v>290</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" s="1">
         <v>0.40625</v>
       </c>
@@ -1194,13 +1440,19 @@
         <v>1200</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41">
         <v>290</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" s="1">
         <v>0.41666666666666702</v>
       </c>
@@ -1214,13 +1466,19 @@
         <v>1200</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42">
         <v>290</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" s="1">
         <v>0.42708333333333298</v>
       </c>
@@ -1234,13 +1492,19 @@
         <v>1200</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43">
         <v>290</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" s="1">
         <v>0.4375</v>
       </c>
@@ -1254,13 +1518,19 @@
         <v>1200</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
         <v>290</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" s="1">
         <v>0.44791666666666702</v>
       </c>
@@ -1274,13 +1544,19 @@
         <v>1200</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
         <v>290</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A46" s="1">
         <v>0.45833333333333298</v>
       </c>
@@ -1294,13 +1570,19 @@
         <v>1200</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46">
         <v>290</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A47" s="1">
         <v>0.46875</v>
       </c>
@@ -1314,13 +1596,19 @@
         <v>1200</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F47">
         <v>290</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A48" s="1">
         <v>0.47916666666666702</v>
       </c>
@@ -1334,13 +1622,19 @@
         <v>1200</v>
       </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48">
         <v>290</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A49" s="1">
         <v>0.48958333333333298</v>
       </c>
@@ -1354,13 +1648,19 @@
         <v>1200</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F49">
         <v>290</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A50" s="1">
         <v>0.5</v>
       </c>
@@ -1374,13 +1674,19 @@
         <v>1200</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50">
         <v>290</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A51" s="1">
         <v>0.51041666666666696</v>
       </c>
@@ -1394,13 +1700,19 @@
         <v>800</v>
       </c>
       <c r="E51">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <v>290</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A52" s="1">
         <v>0.52083333333333304</v>
       </c>
@@ -1414,13 +1726,19 @@
         <v>800</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F52">
         <v>290</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A53" s="1">
         <v>0.53125</v>
       </c>
@@ -1434,13 +1752,19 @@
         <v>800</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53">
         <v>290</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A54" s="1">
         <v>0.54166666666666696</v>
       </c>
@@ -1454,13 +1778,19 @@
         <v>800</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F54">
         <v>290</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A55" s="1">
         <v>0.55208333333333304</v>
       </c>
@@ -1474,13 +1804,19 @@
         <v>800</v>
       </c>
       <c r="E55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F55">
         <v>290</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A56" s="1">
         <v>0.5625</v>
       </c>
@@ -1494,13 +1830,19 @@
         <v>800</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
         <v>290</v>
       </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A57" s="1">
         <v>0.57291666666666696</v>
       </c>
@@ -1514,13 +1856,19 @@
         <v>800</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F57">
         <v>290</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A58" s="1">
         <v>0.58333333333333304</v>
       </c>
@@ -1534,13 +1882,19 @@
         <v>800</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58">
         <v>290</v>
       </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A59" s="1">
         <v>0.59375</v>
       </c>
@@ -1554,13 +1908,19 @@
         <v>1200</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F59">
         <v>290</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A60" s="1">
         <v>0.60416666666666696</v>
       </c>
@@ -1574,13 +1934,19 @@
         <v>1200</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60">
         <v>290</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A61" s="1">
         <v>0.61458333333333304</v>
       </c>
@@ -1594,13 +1960,19 @@
         <v>1200</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F61">
         <v>290</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A62" s="1">
         <v>0.625</v>
       </c>
@@ -1614,13 +1986,19 @@
         <v>1200</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F62">
         <v>290</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A63" s="1">
         <v>0.63541666666666696</v>
       </c>
@@ -1634,13 +2012,19 @@
         <v>1200</v>
       </c>
       <c r="E63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F63">
         <v>290</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A64" s="1">
         <v>0.64583333333333304</v>
       </c>
@@ -1654,13 +2038,19 @@
         <v>1200</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64">
         <v>290</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A65" s="1">
         <v>0.65625</v>
       </c>
@@ -1674,13 +2064,19 @@
         <v>1200</v>
       </c>
       <c r="E65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F65">
         <v>290</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A66" s="1">
         <v>0.66666666666666696</v>
       </c>
@@ -1694,13 +2090,19 @@
         <v>1200</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F66">
         <v>290</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A67" s="1">
         <v>0.67708333333333304</v>
       </c>
@@ -1714,13 +2116,19 @@
         <v>1200</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>290</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A68" s="1">
         <v>0.6875</v>
       </c>
@@ -1734,13 +2142,19 @@
         <v>1200</v>
       </c>
       <c r="E68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F68">
         <v>290</v>
       </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A69" s="1">
         <v>0.69791666666666696</v>
       </c>
@@ -1754,13 +2168,19 @@
         <v>1200</v>
       </c>
       <c r="E69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F69">
         <v>290</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A70" s="1">
         <v>0.70833333333333304</v>
       </c>
@@ -1774,13 +2194,19 @@
         <v>1200</v>
       </c>
       <c r="E70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F70">
         <v>290</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A71" s="1">
         <v>0.71875</v>
       </c>
@@ -1794,13 +2220,19 @@
         <v>1200</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71">
         <v>290</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A72" s="1">
         <v>0.72916666666666696</v>
       </c>
@@ -1814,13 +2246,19 @@
         <v>1200</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72">
         <v>290</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A73" s="1">
         <v>0.73958333333333304</v>
       </c>
@@ -1834,13 +2272,19 @@
         <v>1200</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73">
         <v>290</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A74" s="1">
         <v>0.75</v>
       </c>
@@ -1854,13 +2298,19 @@
         <v>1200</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74">
         <v>290</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A75" s="1">
         <v>0.76041666666666696</v>
       </c>
@@ -1874,13 +2324,19 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F75">
         <v>290</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A76" s="1">
         <v>0.77083333333333304</v>
       </c>
@@ -1894,13 +2350,19 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76">
         <v>290</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A77" s="1">
         <v>0.78125</v>
       </c>
@@ -1914,13 +2376,19 @@
         <v>0</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77">
         <v>290</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A78" s="1">
         <v>0.79166666666666696</v>
       </c>
@@ -1934,13 +2402,19 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F78">
         <v>290</v>
       </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A79" s="1">
         <v>0.80208333333333304</v>
       </c>
@@ -1954,13 +2428,19 @@
         <v>0</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F79">
         <v>290</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A80" s="1">
         <v>0.8125</v>
       </c>
@@ -1974,13 +2454,19 @@
         <v>0</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80">
         <v>290</v>
       </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A81" s="1">
         <v>0.82291666666666696</v>
       </c>
@@ -1994,13 +2480,19 @@
         <v>0</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81">
         <v>290</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A82" s="1">
         <v>0.83333333333333304</v>
       </c>
@@ -2014,13 +2506,19 @@
         <v>0</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82">
         <v>290</v>
       </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A83" s="1">
         <v>0.84375</v>
       </c>
@@ -2034,13 +2532,19 @@
         <v>0</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F83">
         <v>290</v>
       </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A84" s="1">
         <v>0.85416666666666696</v>
       </c>
@@ -2054,13 +2558,19 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84">
         <v>290</v>
       </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A85" s="1">
         <v>0.86458333333333304</v>
       </c>
@@ -2074,13 +2584,19 @@
         <v>0</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85">
         <v>288</v>
       </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A86" s="1">
         <v>0.875</v>
       </c>
@@ -2094,13 +2610,19 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86">
         <v>288</v>
       </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A87" s="1">
         <v>0.88541666666666696</v>
       </c>
@@ -2114,13 +2636,19 @@
         <v>0</v>
       </c>
       <c r="E87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F87">
         <v>288</v>
       </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A88" s="1">
         <v>0.89583333333333304</v>
       </c>
@@ -2134,13 +2662,19 @@
         <v>0</v>
       </c>
       <c r="E88">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F88">
         <v>288</v>
       </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A89" s="1">
         <v>0.90625</v>
       </c>
@@ -2154,13 +2688,19 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F89">
         <v>288</v>
       </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A90" s="1">
         <v>0.91666666666666696</v>
       </c>
@@ -2174,13 +2714,19 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>288</v>
       </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A91" s="1">
         <v>0.92708333333333304</v>
       </c>
@@ -2194,13 +2740,19 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91">
         <v>288</v>
       </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A92" s="1">
         <v>0.9375</v>
       </c>
@@ -2214,13 +2766,19 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92">
         <v>288</v>
       </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A93" s="1">
         <v>0.94791666666666696</v>
       </c>
@@ -2234,13 +2792,19 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F93">
         <v>288</v>
       </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A94" s="1">
         <v>0.95833333333333304</v>
       </c>
@@ -2254,13 +2818,19 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F94">
         <v>288</v>
       </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A95" s="1">
         <v>0.96875</v>
       </c>
@@ -2274,13 +2844,19 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F95">
         <v>288</v>
       </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A96" s="1">
         <v>0.97916666666666696</v>
       </c>
@@ -2294,13 +2870,19 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96">
         <v>288</v>
       </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A97" s="1">
         <v>0.98958333333333304</v>
       </c>
@@ -2314,972 +2896,978 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97">
         <v>288</v>
       </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A98" s="1"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
